--- a/data_extactor/batch_10_fa/batch_0058_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0058_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | انعطاف‌پذیری بدنی | قدرت بالاتنه | ثبات دست و بازو</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>فضاهای داخلی، دارای کنترل دما | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پاک‌کنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | آشپزهای فست‌فود | آشپزهای سفارش‌های سریع | خدمه سالن غذاخوری و سلف‌سرویس و کمک‌بارتندرها | کارکنان فست‌فود و پیشخوان | اپراتورها و متصدیان ماشین‌های پخت غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا، غیررستورانی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | دستیاران--کارگران تولید | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، موجودی و مواد | کارگران خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و تمیزکنندگان خانه‌داری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکننده | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارگران بازیافت و احیاء</t>
+          <t>تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | آشپزهای غذای آماده | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارگران فست فود و پیشخوان | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | کمک‌کاران--کارگران تولید | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و تمیزکنندگان خانه‌داری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارگران بازیافت و احیا</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای داخلی، دارای کنترل دما | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای پیاده‌روی یا دویدن | گفتگوهای تلفنی | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان بیرونی یا عموم مردم به طور کلی | اهمیت دقیق یا درست بودن کار | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناراحت، عصبانی یا بی‌ادب</t>
+          <t>صرف زمان برای ایستادن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | مکالمات تلفنی | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | دربان‌ها | آشپزهای خانگی شخصی | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | خدمه سالن غذاخوری و سلف‌سرویس و کمک‌بارتندرها | کارکنان فست‌فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | متصدیان مسافران | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌های زن و مرد</t>
+          <t>باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | کانسرج‌ها | آشپزهای خانگی خصوصی | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | متصدیان مسافران | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت بدنی | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | فضاهای داخلی، بدون کنترل دما | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف مشابه | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن کار | صرف زمان برای پیاده‌روی یا دویدن | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان بیرونی یا عموم مردم به طور کلی</t>
+          <t>صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران آماده‌سازی غذا | کارکنان فست‌فود و پیشخوان | خدمه سالن غذاخوری و سلف‌سرویس و کمک‌بارتندرها | ظرف‌شوی‌ها | سروکنندگان غذا، غیررستورانی | پیشخدمت‌های زن و مرد | باریستاها | بارتندرها | میزبانان رستوران، سالن و کافی‌شاپ | آشپزهای فست‌فود | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای رستوران | آشپزهای سفارش‌های سریع | آشپزها، سایر موارد | سرآشپزها و آشپزهای ارشد | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | مدیران خدمات غذایی | صندوق‌داران | کارمندان پیشخوان و اجاره | متصدیان تفریحات و سرگرمی</t>
+          <t>کارگران آماده‌سازی مواد غذایی | کارگران فست فود و پیشخوان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | سروکنندگان غذا، غیررستورانی | پیشخدمت‌ها و گارسون‌ها | باریستاها | بارتندرها | میزبانان رستوران، سالن و کافی‌شاپ | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های فوری | آشپزها، سایر موارد | سرآشپزها و آشپزهای ارشد | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | مدیران خدمات غذایی | صندوق‌داران | کارمندان باجه و اجاره | متصدیان تفریح و سرگرمی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن گفتن | گوش دادن فعال | تفکر انتقادی | استراتژی‌های یادگیری | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امور اداری و مدیریت | آموزش و پرورش | امنیت و ایمنی عمومی | پرسنل و منابع انسانی | اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | درک کتبی | بینایی دور | چالاکی دست | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | درک کتبی | بینایی دور | مهارت دستی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | فضاهای داخلی، دارای کنترل دما | گفتگوهای تلفنی | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | فشار زمانی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن کار | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | صرف زمان برای پیاده‌روی یا دویدن | آزادی در تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | فشار زمانی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران تاسیسات | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول متصدیان مسافران | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران کل و عملیاتی | خدمتکاران و تمیزکنندگان خانه‌داری | هماهنگ‌کنندگان بازیافت</t>
+          <t>مدیران خدمات اداری | مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | خدمتکاران و تمیزکنندگان خانه‌داری | هماهنگ‌کنندگان بازیافت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | استراتژی‌های یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امور اداری و مدیریت | ریاضیات | امنیت و ایمنی عمومی | پرسنل و منابع انسانی | مکانیک | آموزش و پرورش | شیمی | ساختمان و ساخت‌وساز | طراحی | اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | آموزش و پرورش | شیمی | ساختمان و ساخت‌وساز | طراحی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | درک کتبی | تجسم فضایی | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | استدلال قیاسی | بیان کتبی | روان بودن ایده‌ها | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | چالاکی انگشتان | چالاکی دست | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | درک کتبی | تجسم | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | استدلال قیاسی | بیان کتبی | روانی ایده‌ها | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فضاهای بیرونی، قرار گرفتن در معرض تمامی شرایط آب و هوایی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | گفتگوهای تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | ایمیل | تعامل با مشتریان بیرونی یا عموم مردم به طور کلی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن کار | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | صرف زمان برای پیاده‌روی یا دویدن | پیامد خطا | نزدیکی فیزیکی | موقعیت‌های درگیری</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | پیامد خطا | نزدیکی فیزیکی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی عمران | مدیران ساخت‌وساز | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول متصدیان مسافران | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارکنان امنیتی | تکنسین‌های جنگل‌داری و حفاظت | مدیران کل و عملیاتی | کارگران فضای سبز و نگهداری محوطه | کارگران تعمیر و نگهداری، عمومی | مدیران نصب سیستم‌های انرژی خورشیدی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی عمران | مدیران ساخت‌وساز | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | تکنسین‌های جنگل و حفاظت | مدیران عمومی و عملیات | کارگران فضای سبز و نگهداری محوطه | کارگران نگهداری و تعمیرات عمومی | مدیران نصب انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | امور اداری و مدیریت</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | بینایی نزدیک | انعطاف‌پذیری بدنی | قدرت ایستا | چالاکی دست | ثبات دست و بازو | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | مهارت دستی | ثبات دست و بازو | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای پیاده‌روی یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای داخلی، دارای کنترل دما | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای راه رفتن یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصب‌کنندگان فرش | پاک‌کنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | کارگران ساختمانی | ظرف‌شوی‌ها | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سنباده‌زن‌ها و پرداخت‌کنندگان کف | پرداخت‌کنندگان مبلمان | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | دستیاران--نقاشان، کاغذدیوارکن‌ها، گچ‌کاران و بناهای سیمان‌کار | کارگران و جابجا‌کنندگان دستی بار، موجودی و مواد | کارگران فضای سبز و نگهداری محوطه | کارگران خشک‌شویی و لباس‌شویی | خدمتکاران و تمیزکنندگان خانه‌داری | کارگران تعمیر و نگهداری، عمومی | کارگران بازیافت و احیاء | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله‌های فاضلاب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>نصّابان موکت و فرش | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | کارگران ساختمانی | ظرف‌شوی‌ها | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سنباده‌کاران و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران فضای سبز و نگهداری محوطه | کارکنان خشک‌شویی و لباس‌شویی | خدمتکاران و تمیزکنندگان خانه‌داری | کارگران نگهداری و تعمیرات عمومی | کارگران بازیافت و احیا | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امنیت و ایمنی عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | بینایی نزدیک | انعطاف‌پذیری بدنی | استقامت بدنی | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای انجام حرکات تکراری | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان برای خم شدن یا چرخاندن بدن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای داخلی، دارای کنترل دما | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن کار | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نصب‌کنندگان فرش | پاک‌کنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | خدمه سالن غذاخوری و سلف‌سرویس و کمک‌بارتندرها | ظرف‌شوی‌ها | کارکنان فست‌فود و پیشخوان | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سنباده‌زن‌ها و پرداخت‌کنندگان کف | کارگران آماده‌سازی غذا | سروکنندگان غذا، غیررستورانی | پرداخت‌کنندگان مبلمان | دستیاران--نقاشان، کاغذدیوارکن‌ها، گچ‌کاران و بناهای سیمان‌کار | دستیاران--کارگران تولید | کارمندان پذیرش هتل، متل و اقامتگاه | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران خشک‌شویی و لباس‌شویی | متصدیان رختکن، اتاق لباس و اتاق پرو | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | اتوکنندگان منسوجات، پوشاک و مواد مرتبط | کارگران بازیافت و احیاء</t>
+          <t>نصّابان موکت و فرش | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سنباده‌کاران و پرداخت‌کاران کف | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | پرداخت‌کاران مبلمان | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | کمک‌کاران--کارگران تولید | کارمندان پذیرش هتل، متل و اقامتگاه | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارکنان خشک‌شویی و لباس‌شویی | متصدیان رختکن، اتاق لباس و اتاق پرو | کارگران نقاشی، پوشش‌دهی و تزیین | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارگران بازیافت و احیا</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | شیمی | امنیت و ایمنی عمومی | امور اداری و مدیریت | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت بدنی | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | فضاهای داخلی، بدون کنترل دما | اهمیت تکرار وظایف مشابه | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | خدمتکاران و تمیزکنندگان خانه‌داری | سرپرستان خط اول کارگران خانه‌داری و سرایداری | کارگران کنترل آفات | کارگران فضای سبز و نگهداری محوطه | کارگران نگهداری محوطه، سایر موارد | کارگران حذف مواد خطرناک | کارگران خشک‌شویی و لباس‌شویی | کارگران تعمیر و نگهداری، عمومی | مدیران تاسیسات | دستیاران--کارگران نصب، تعمیر و نگهداری | اپراتورهای کامیون و تراکتور صنعتی | کارگران و جابجا‌کنندگان دستی بار، موجودی و مواد | پاک‌کنندگان وسایل نقلیه و تجهیزات | کارگران بازیافت و احیاء | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | نگهبانان امنیتی | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | جابجاکنندگان، اسپری‌کنندگان و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله‌های فاضلاب</t>
+          <t>سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | خدمتکاران و تمیزکنندگان خانه‌داری | سرپرستان خط اول کارگران خانه‌داری و سرایداری | کارگران کنترل آفات | کارگران فضای سبز و نگهداری محوطه | کارگران نگهداری فضای سبز، سایر | کارگران حذف مواد خطرناک | کارکنان خشک‌شویی و لباس‌شویی | کارگران نگهداری و تعمیرات عمومی | مدیران تسهیلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران بازیافت و احیا | جمع‌آوران زباله و مواد بازیافتی | نگهبانان امنیتی | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Intuit QuickBooks | Marathon Data Systems PestPac | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft SharePoint | Microsoft Word | نرم‌افزار گزارش‌نویسی | نرم‌افزار موجودی لوازم | نرم‌افزار برنامه‌ریزی کار | YouTube</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Intuit QuickBooks | Marathon Data Systems PestPac | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft SharePoint | Microsoft Word | نرم‌افزار گزارش‌نویسی | نرم‌افزار موجودی لوازم | نرم‌افزار زمان‌بندی کار | YouTube</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | نگارش | مانیتورینگ | سخن گفتن | یادگیری فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | امنیت و ایمنی عمومی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | بینایی دور | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | انعطاف‌پذیری بدنی | قدرت بالاتنه | دقت کنترل | چالاکی دست | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | تجسم فضایی | تشخیص رنگ بصری</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | بینایی دور | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | دقت کنترل | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | تجسم | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضاهای بیرونی، قرار گرفتن در معرض تمامی شرایط آب و هوایی | گفتگوهای تلفنی | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن کار | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان بیرونی یا عموم مردم به طور کلی | صرف زمان برای پیاده‌روی یا دویدن | صرف زمان به صورت ایستاده | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | متخصصان بازسازی مناطق صنعتی متروکه و مدیران سایت | بازرسان ساخت‌وساز و ساختمان | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | کارگران کشاورزی و کارگران ساده، زراعت، خزانه‌داری و گلخانه | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | کارگران حذف مواد خطرناک | کارگران نگهداری بزرگراه | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران فضای سبز و نگهداری محوطه | کارگران تعمیر و نگهداری، عمومی | متخصصان بهداشت و ایمنی شغلی | جابجاکنندگان، اسپری‌کنندگان و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله‌های فاضلاب | دانشمندان خاک و گیاه | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | بازرسان ساختمان و ساخت‌وساز | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | کارگران حذف مواد خطرناک | کارگران نگهداری بزرگراه‌ها | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران فضای سبز و نگهداری محوطه | کارگران نگهداری و تعمیرات عمومی | متخصصان بهداشت و ایمنی شغلی | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | دانشمندان خاک و گیاه | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو | چالاکی دست | قدرت بالاتنه | ثبات دست و بازو | انعطاف‌پذیری بدنی | قدرت ایستا | دقت کنترل | بینایی نزدیک | استقامت بدنی | تجسم فضایی | حساسیت به مسئله</t>
+          <t>هماهنگی چند عضو | مهارت دستی | قدرت تنه | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | دقت کنترل | بینایی نزدیک | استقامت | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضاهای بیرونی، قرار گرفتن در معرض تمامی شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | صرف زمان برای پیاده‌روی یا دویدن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه روباز یا کار با تجهیزات | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه روباز یا کار با تجهیزات | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | بناهای سیمان‌کار و پرداخت‌کنندگان بتن | کارگران ساختمانی | درخت‌اندازها | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | کارگران کشاورزی و کارگران ساده، زراعت، خزانه‌داری و گلخانه | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | کارگران جنگل‌داری و حفاظت | دستیاران--نقاشان، کاغذدیوارکن‌ها، گچ‌کاران و بناهای سیمان‌کار | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی، اتصالات لوله و بخارکاران | کارگران نگهداری بزرگراه | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران تعمیر و نگهداری، عمومی | مهندسان عملیاتی و سایر اپراتورهای تجهیزات ساخت‌وساز | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | جابجاکنندگان، اسپری‌کنندگان و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخارکاران | کارگران ساده، نفت و گاز | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله‌های فاضلاب | هرس‌کنندگان و آرایش‌دهندگان درخت</t>
+          <t>اپراتورهای تجهیزات کشاورزی | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | قطع‌کنندگان درختان | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | کارگران جنگل و حفاظت | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران نگهداری بزرگراه‌ها | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران نگهداری و تعمیرات عمومی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران فنی همه‌کاره نفت و گاز | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | هرس‌کنندگان و شاخه‌زن‌های درختان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0058_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0058_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | انعطاف‌پذیری بدن | قدرت بدنی بالاتنه | ثبات دست و بازو</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایستادن طولانی‌مدت حین کار | استفاده مستمر از دست‌ها برای کار با ابزارها | توجه به ایمنی و بهداشت سایر کارکنان | محیط سرپوشیده با تهویهٔ مطبوع | کار گروهی و تیمی | گفت‌وگوی حضوری با همکاران | ارتباط مداوم با دیگران</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نظافتچیان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | آشپزهای فست‌فود | آشپزهای پخت سریع | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | کارکنان کانتر و فست‌فود | اپراتورها و متصدیان دستگاه‌های پخت غذا | کارگران آماده‌سازی غذا | مهمانداران سرو غذا در مراکز غیررستورانی | اپراتورها و متصدیان دستگاه‌های تفت، پخت و خشک‌کردن مواد غذایی و توتون | کارگران ساده بخش تولید | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران ساده جابه‌جایی دستی بار و کالا | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچیان منازل و هتل‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اختلاط و ترکیب مواد | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | کارگران دستی بسته‌بندی | کارگران تفکیک و بازیافت مواد</t>
+          <t>شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | آشپزان غذاهای فوری و فست‌فود | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کمک‌کارگران خطوط تولید | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچیان منازل و هتل‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | کارگران بازیافت و تفکیک پسماند</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | دید نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>باریستاها | متصدیان بار | صندوقداران | سرآشپزها و آشپزهای ارشد | راهنما و متصدی خدمات مهمانان (کانسیرژ) | آشپزهای منازل خصوصی | معرفی‌کنندگان و تبلیغ‌کنندگان کالا | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | کارکنان کانتر و فست‌فود | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مهمانداران سرو غذا در مراکز غیررستورانی | مدیران خدمات پذیرایی و غذا | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان رختکن و اتاق تعویض لباس | مدیران مراکز اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مهمانداران و راهنمایان مسافران | راهنمایان سالن، متصدیان ورودی و بلیت‌گیرها | سالن‌کاران و گارسون‌ها</t>
+          <t>باریستاها | متصدیان بار و نوشیدنی | صندوق‌داران | سرآشپزان و آشپزان ارشد | متصدیان تشریفات و خدمات میهمانان | آشپزان منازل مسکونی و سرآشپزان شخصی | معرفی‌کنندگان و مروجان کالا | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | مدیران هتل و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مهمانداران و متصدیان خدمات مسافران | راهنماها، متصدیان سالن و بلیط‌گیرها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | تولید و فراوری | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چندعضو | دقت کنترل | قدرت ایستا | قدرت بدنی بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدن | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران آماده‌سازی غذا | کارکنان کانتر و فست‌فود | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | ظرف‌شویان | مهمانداران سرو غذا در مراکز غیررستورانی | سالن‌کاران و گارسون‌ها | باریستاها | متصدیان بار | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | آشپزهای فست‌فود | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای رستوران | آشپزهای پخت سریع | سایر آشپزها | سرآشپزها و آشپزهای ارشد | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | مدیران خدمات پذیرایی و غذا | صندوقداران | کارمندان کانتر و تحویل | متصدیان مراکز تفریحی و شهربازی‌ها</t>
+          <t>کارگران آماده‌سازی غذا | کارگران پیشخوان و فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سروکنندگان غذا در محیط‌های غیررستورانی | پیش‌خدمتان و گارسون‌ها | باریستاها | متصدیان بار و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | آشپزان غذاهای فوری | سایر آشپزان | سرآشپزان و آشپزان ارشد | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | متصدیان اماکن تفریحی و شهربازی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | آموزش و پرورش | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | بیان کتبی | درک کتبی | دید دور | چابکی دستی | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | درک کتبی | بینایی دور | مهارت دستی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران تاسیسات و نگهداری ساختمان | سرپرستان رده اول مشاغل ساختمانی و استخراج | سرپرستان رده اول کارکنان تفریحی و سرگرمی، به‌جز مراکز قمار | سرپرستان رده اول کارگران کشاورزی، شیلات و جنگلداری | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده اول کمک‌کارگران، کارگران ساده و متصدیان حمل بار دستی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده اول اپراتورهای ماشین‌آلات و خودروهای جابه‌جایی کالا | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول فروشندگان غیرخرده‌فروشی | سرپرستان رده اول کارکنان پشتیبانی دفتری و اداری | سرپرستان رده اول مهمانداران و راهنمایان مسافران | سرپرستان رده اول کارکنان خدمات فردی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده اول فروشندگان خرده‌فروشی | سرپرستان رده اول نیروهای حراست و نگهبانی | مدیران کل و مدیران اجرایی | خدمتکاران و نظافتچیان منازل و هتل‌ها | هماهنگ‌کنندگان امور بازیافت مواد</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | خدمتکاران و نظافتچیان منازل و هتل‌ها | هماهنگ‌کنندگان امور بازیافت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | مکانیک | آموزش و پرورش | شیمی | ساختمان و سازه | طراحی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | آموزش و پرورش | شیمی | ساختمان و ساخت‌وساز | طراحی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | وضوح گفتار | درک کتبی | تجسم فضایی | ثبات دست و بازو | تقسیم توجه | سرعت ادراک | انعطاف‌پذیری ادراک شکل | مرتب‌سازی اطلاعات | دید دور | استدلال استقرایی | استدلال قیاسی | بیان کتبی | روانی ایده‌ها | قدرت ایستا | هماهنگی چندعضو | دقت کنترل | چابکی انگشتان | چابکی دستی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | درک کتبی | تجسم | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بینایی دور | استدلال استقرایی | استدلال قیاسی | بیان کتبی | روانی ایده‌ها | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های مهندسی عمران | مدیران پروژه و ساخت | سرپرستان رده اول مشاغل ساختمانی و استخراج | سرپرستان رده اول کارکنان تفریحی و سرگرمی، به‌جز مراکز قمار | سرپرستان رده اول کارگران کشاورزی، شیلات و جنگلداری | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده اول کمک‌کارگران، کارگران ساده و متصدیان حمل بار دستی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول اپراتورهای ماشین‌آلات و خودروهای جابه‌جایی کالا | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان پشتیبانی دفتری و اداری | سرپرستان رده اول مهمانداران و راهنمایان مسافران | سرپرستان رده اول کارکنان خدمات فردی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده اول نیروهای حراست و نگهبانی | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | مدیران کل و مدیران اجرایی | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی نگهداری و تعمیرات | مدیران نصب سیستم‌های انرژی خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران کل و مدیران عملیات | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی تعمیرات و نگهداری تاسیسات | مدیران اجرای پروژه‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>تی شیشه‌شور و جمع‌کننده آب | Eko | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>تی شیشه‌شور و جمع‌کننده آب | Eko | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | تی شیشه‌شوی</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>قدرت بدنی بالاتنه | دید نزدیک | انعطاف‌پذیری بدن | قدرت ایستا | چابکی دستی | ثبات دست و بازو | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | مهارت دستی | ثبات دست و بازو | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصابان موکت و کف‌پوش | نظافتچیان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و پاشش | کارگران ساختمانی | ظرف‌شویان | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و جلادهندگان مبلمان | کارگران امحا و پاکسازی مواد خطرناک | کارگران ساده بخش استخراج معدن | کارگران ساده نقاشی ساختمان، کاغذدیواری و گچ‌کاری | کارگران ساده جابه‌جایی دستی بار و کالا | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران خشکشویی و رختشویخانه | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران عمومی نگهداری و تعمیرات | کارگران تفکیک و بازیافت مواد | تکنسین‌های تخلیه چاه و لایروبی شبکه فاضلاب | اپراتورهای تصفیه‌خانه و سیستم‌های آب و فاضلاب</t>
+          <t>موکت‌کاران و نصابان فرش | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | کارگران ساختمانی | ظرف‌شویان | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران کمکی استخراج معدن | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران خشکشویی و رختشویخانه | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارگران بازیافت و تفکیک پسماند | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت بدنی بالاتنه | دید نزدیک | انعطاف‌پذیری بدن | استقامت بدنی | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نصابان موکت و کف‌پوش | نظافتچیان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | ظرف‌شویان | کارکنان کانتر و فست‌فود | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | کارگران آماده‌سازی غذا | مهمانداران سرو غذا در مراکز غیررستورانی | پرداخت‌کاران و جلادهندگان مبلمان | کارگران ساده نقاشی ساختمان، کاغذدیواری و گچ‌کاری | کارگران ساده بخش تولید | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران خشکشویی و رختشویخانه | متصدیان رختکن و اتاق تعویض لباس | کارگران نقاشی، پوشش‌دهی و تزیین | اتوکاران پارچه، پوشاک و منسوجات | کارگران تفکیک و بازیافت مواد</t>
+          <t>موکت‌کاران و نصابان فرش | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌کارگران خطوط تولید | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران خشکشویی و رختشویخانه | متصدیان رختکن، امانات و اتاق پرو | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران بازیافت و تفکیک پسماند</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چندعضو | دقت کنترل | قدرت ایستا | قدرت بدنی بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدن | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | کارگران سم‌پاشی و کنترل آفات | کارگران باغبانی، فضای سبز و نگهداری محوطه | سایر کارگران نگهداری و خدمات محوطه | کارگران امحا و پاکسازی مواد خطرناک | کارگران خشکشویی و رختشویخانه | کارگران عمومی نگهداری و تعمیرات | مدیران تاسیسات و نگهداری ساختمان | کمک‌کارگران نصب، نگهداری و تعمیرات | اپراتورهای لیفتراک و تراکتورهای صنعتی | کارگران ساده جابه‌جایی دستی بار و کالا | نظافتچیان وسایل نقلیه و تجهیزات | کارگران تفکیک و بازیافت مواد | کارگران جمع‌آوری پسماند و مواد بازیافتی | نگهبانان و ماموران حفاظتی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌ها در فضای سبز | تکنسین‌های تخلیه چاه و لایروبی شبکه فاضلاب</t>
+          <t>سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | کارگران سم‌پاشی و دفع آفات | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران نگهداری و مراقبت از فضای سبز و محوطه، سایر مشاغل | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران خشکشویی و رختشویخانه | کارگران عمومی تعمیرات و نگهداری تاسیسات | مدیران امور ساختمان و تأسیسات | کارگران کمکی نصب، نگهداری و تعمیرات | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران بازیافت و تفکیک پسماند | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | نگهبانان و ماموران حراست | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | دید دور | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری ادراک شکل | انعطاف‌پذیری بدن | قدرت بدنی بالاتنه | دقت کنترل | چابکی دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | تجسم فضایی | تمایز رنگ‌ها</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | بینایی دور | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | دقت کنترل | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | تجسم | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | کارشناسان و مدیران بازسازی اراضی صنعتی متروکه | بازرسان ساختمان و سازه | تکنسین‌ها و کاردان‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | کارگران مزارع، زراعت، نهالستان و گلخانه | سرپرستان رده اول کارگران کشاورزی، شیلات و جنگلداری | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران امحا و پاکسازی مواد خطرناک | کارگران نگهداری و راهداری جاده‌ها | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی نگهداری و تعمیرات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | سم‌پاشان و متصدیان کاربرد آفت‌کش‌ها در فضای سبز | تکنسین‌های تخلیه چاه و لایروبی شبکه فاضلاب | دانشمندان علوم خاک و گیاه‌شناسی | اپراتورهای تصفیه‌خانه و سیستم‌های آب و فاضلاب</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های کشاورزی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | بازرسان ساخت‌وساز و ساختمان | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران راهداری و نگهداری جاده‌ها | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | متخصصان خاک‌شناسی و علوم گیاهی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IBM Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Facebook</t>
+          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Office | Microsoft Windows | Facebook</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضو | چابکی دستی | قدرت بدنی بالاتنه | ثبات دست و بازو | انعطاف‌پذیری بدن | قدرت ایستا | دقت کنترل | دید نزدیک | استقامت بدنی | تجسم فضایی | حساسیت به مسئله</t>
+          <t>هماهنگی چند عضو | مهارت دستی | قدرت تنه | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | دقت کنترل | بینایی نزدیک | استقامت | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات کشاورزی | بناها و پرداخت‌کاران بتن | کارگران ساختمانی | کارگران درخت‌بری و قطع درختان جنگلی | مکانیک‌ها و تکنسین‌های تعمیر ماشین‌آلات کشاورزی | کارگران مزارع، زراعت، نهالستان و گلخانه | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران جنگلداری و حفاظت منابع طبیعی | کارگران ساده نقاشی ساختمان، کاغذدیواری و گچ‌کاری | کارگران ساده لوله‌کشی و خطوط انتقال آب و گاز | کارگران نگهداری و راهداری جاده‌ها | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران عمومی نگهداری و تعمیرات | مهندسان ماشین‌آلات و اپراتورهای تجهیزات سنگین ساختمانی | اپراتورهای دستگاه‌های روسازی، آسفالت و غلتک‌کوبی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌ها در فضای سبز | لوله‌کشان و نصابان خطوط لوله و تاسیسات بخار | کارگران ساده دکل و حفاری نفت و گاز | تکنسین‌های تخلیه چاه و لایروبی شبکه فاضلاب | هرس‌کاران و شاخه‌زن‌های درختان</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | درخت‌اندازان و چوب‌بُران جنگل | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران راهداری و نگهداری جاده‌ها | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران عمومی تعمیرات و نگهداری تاسیسات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران عمومی سکو و میادین نفت و گاز | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
